--- a/research/alameda/deliverables/Oakland_Business_HardInquiry_v1.xlsx
+++ b/research/alameda/deliverables/Oakland_Business_HardInquiry_v1.xlsx
@@ -501,9 +501,7 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr"/>
-    </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -657,9 +655,7 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr"/>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>

--- a/research/alameda/deliverables/Oakland_Business_HardInquiry_v1.xlsx
+++ b/research/alameda/deliverables/Oakland_Business_HardInquiry_v1.xlsx
@@ -501,7 +501,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -655,7 +654,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
@@ -1608,12 +1606,12 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Elan</t>
+          <t>RAIL CONFLICT: Elan (mbonlineportal) vs TCM (mycommunitycc/FROlvrV1uR72) — unresolved</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>follows-rail</t>
+          <t>UNKNOWN — if Elan≈TU-usual; if TCM, bureau undocumented. Confirm at application</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">

--- a/research/alameda/deliverables/Oakland_Business_HardInquiry_v1.xlsx
+++ b/research/alameda/deliverables/Oakland_Business_HardInquiry_v1.xlsx
@@ -501,6 +501,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -654,6 +655,7 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
@@ -1263,7 +1265,11 @@
       <c r="K10" s="3" t="inlineStr"/>
       <c r="L10" s="3" t="inlineStr"/>
       <c r="M10" s="3" t="inlineStr"/>
-      <c r="N10" s="3" t="inlineStr"/>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>MIXED PROGRAM (corrected 2026-07-26): the One Card (corporate/business) is Elan per East West's own page — "The creditor and issuer of the East West Bank One Card is Elan Financial Services, pursuant to a license from Visa U.S.A." BUT East West SELF-ISSUES its Secured Visa Classic (consumer; Elan not named) and books $4,631K of credit-card loans on its own balance sheet (FDIC call report 2026-03-31, CERT 31628). Do NOT label the bank flatly "Elan".</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
